--- a/documents/Task.xlsx
+++ b/documents/Task.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="33">
   <si>
     <t>Sr.no</t>
   </si>
@@ -386,7 +386,44 @@
     - Improve the animation of side bar in windows screen.</t>
   </si>
   <si>
-    <t>animation removed of side bar for android</t>
+    <t>Update animation of side bar for android (Working)</t>
+  </si>
+  <si>
+    <t>Pages - 
+    - Added User signup page and connected to the user signup button on login page.
+    - Removed Tenant Signup button from login page.
+    - Test signup feature.
+    - Added Back button to the Tenant Signip page.
+    - Added animation to the user signup page.</t>
+  </si>
+  <si>
+    <t>Code
+    - Code Review and removing unwanted code.
+Component Reviewd,Commented and finilized for code push
+    - Login
+    - Header
+    - User signup
+    - Dashboard/Overview
+    - Dashboard/Porperties
+    - Dashboard/Porperties/Add-Property
+    - Dashboard/Rooms
+    - Dashboard/Add-Room
+    - Dashboard/Room-Details
+    - Dashboard/Tenants
+    - Dashboard/Add-Tenant
+    - Dashboard/Tenant-Details
+    - Dashboard/Billing
+    - Dashboard/Billing/pending
+    - Dashboard/Billing/generated
+    - Dashboard/Billing/generate-bill
+    - Dashboard/Billing/bill-details
+Update error messages for login form
+    - Login component
+    - User signup component
+    - Add property component
+    - Add room component
+    - Add tenant component
+Added Location service to user signup component.</t>
   </si>
 </sst>
 </file>
@@ -430,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -464,6 +501,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -802,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="6.26953125" customWidth="1"/>
@@ -840,16 +883,16 @@
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="20">
+      <c r="C2" s="22">
         <v>46248</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="24">
         <v>46250</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>15</v>
       </c>
     </row>
@@ -860,10 +903,10 @@
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
@@ -881,7 +924,7 @@
       <c r="E4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="19"/>
+      <c r="F4" s="21"/>
     </row>
     <row r="5" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A5" s="6">
@@ -899,7 +942,7 @@
       <c r="E5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="19"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:6" ht="116" x14ac:dyDescent="0.35">
       <c r="A6" s="6">
@@ -917,7 +960,7 @@
       <c r="E6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="19"/>
+      <c r="F6" s="21"/>
     </row>
     <row r="7" spans="1:6" ht="145" x14ac:dyDescent="0.35">
       <c r="A7" s="6">
@@ -935,7 +978,7 @@
       <c r="E7" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="19"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="6">
@@ -953,7 +996,7 @@
       <c r="E8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="19"/>
+      <c r="F8" s="21"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="6">
@@ -971,7 +1014,7 @@
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="19"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" spans="1:6" ht="174" x14ac:dyDescent="0.35">
       <c r="A10" s="6">
@@ -989,7 +1032,7 @@
       <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="19"/>
+      <c r="F10" s="21"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="6"/>
@@ -1005,7 +1048,7 @@
       <c r="E11" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="19" t="s">
+      <c r="F11" s="21" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1025,7 +1068,7 @@
       <c r="E12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="19"/>
+      <c r="F12" s="21"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="6">
@@ -1043,7 +1086,7 @@
       <c r="E13" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="19"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A14" s="6">
@@ -1061,7 +1104,7 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="19"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:6" s="11" customFormat="1" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A15" s="6">
@@ -1079,7 +1122,7 @@
       <c r="E15" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="19"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:6" s="11" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="6"/>
@@ -1093,7 +1136,7 @@
       <c r="E16" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F16" s="19"/>
+      <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="6">
@@ -1111,7 +1154,7 @@
       <c r="E17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="19"/>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A18" s="6">
@@ -1149,7 +1192,7 @@
       <c r="E19" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="19" t="s">
+      <c r="F19" s="21" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1169,7 +1212,7 @@
       <c r="E20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="19"/>
+      <c r="F20" s="21"/>
     </row>
     <row r="21" spans="1:6" ht="87" x14ac:dyDescent="0.35">
       <c r="A21" s="6">
@@ -1187,7 +1230,7 @@
       <c r="E21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="19"/>
+      <c r="F21" s="21"/>
     </row>
     <row r="22" spans="1:6" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A22" s="6">
@@ -1205,7 +1248,7 @@
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="19"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="6">
@@ -1223,23 +1266,45 @@
       <c r="E23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F23" s="19"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="6"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="6"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F23" s="21"/>
+    </row>
+    <row r="24" spans="1:6" ht="87" x14ac:dyDescent="0.35">
+      <c r="A24" s="6">
+        <v>21</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" s="19">
+        <v>46275</v>
+      </c>
+      <c r="D24" s="19">
+        <v>46275</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="391.5" x14ac:dyDescent="0.35">
+      <c r="A25" s="6">
+        <v>22</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="19">
+        <v>46280</v>
+      </c>
+      <c r="D25" s="20">
+        <v>46281</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="21"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="6"/>
@@ -1297,8 +1362,123 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A33" s="6"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A34" s="6"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A35" s="6"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A36" s="6"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A37" s="6"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A38" s="6"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A39" s="6"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A40" s="6"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A41" s="6"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A42" s="6"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A43" s="6"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A44" s="6"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A45" s="6"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A46" s="6"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A47" s="6"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A48" s="6"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A49" s="6"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A50" s="6"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A51" s="6"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A52" s="6"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A53" s="6"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A54" s="6"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A55" s="6"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A56" s="6"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A57" s="6"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A58" s="6"/>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A59" s="6"/>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A60" s="6"/>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A61" s="6"/>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A62" s="6"/>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A63" s="6"/>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A64" s="6"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A65" s="6"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A66" s="6"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A67" s="6"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A68" s="6"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A69" s="6"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A70" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
+    <mergeCell ref="F24:F25"/>
     <mergeCell ref="F19:F23"/>
     <mergeCell ref="F11:F17"/>
     <mergeCell ref="C2:C3"/>
